--- a/cadence-all+分工0817.xlsx
+++ b/cadence-all+分工0817.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2401-测试性\3-核查准则\2507-准则二次调整\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\python_projects\testability_projects\extract_cadence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FFCFB7-AE80-4F2A-9058-CC5C508AF5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FA419A-D444-4D67-A6AC-D739135F3DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{BB04B728-E11B-4EC9-98F8-D9C6CE0BEA09}"/>
+    <workbookView xWindow="375" yWindow="390" windowWidth="18810" windowHeight="14685" xr2:uid="{BB04B728-E11B-4EC9-98F8-D9C6CE0BEA09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -1879,7 +1879,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1975,13 +1975,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1997,7 +1990,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2020,6 +2013,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2027,7 +2116,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2048,9 +2137,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2065,13 +2151,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2089,12 +2169,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2117,12 +2191,533 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 3" xfId="1" xr:uid="{85DA641C-9EE7-433F-8AB7-95C611A02132}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2141,10 +2736,34 @@
 </personList>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C82814D6-0517-495D-8660-1A2DF0AAB23F}" name="表1" displayName="表1" ref="A1:I91" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11" headerRowCellStyle="常规 3" dataCellStyle="常规 3">
+  <autoFilter ref="A1:I91" xr:uid="{C82814D6-0517-495D-8660-1A2DF0AAB23F}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="赵"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{62A88ABC-EA3E-4532-BDB6-247E294352F0}" name="准则序号" dataDxfId="10" dataCellStyle="常规 3"/>
+    <tableColumn id="2" xr3:uid="{66B3F8B8-F331-4388-ACF8-E6FD67AF1DDC}" name="类别" dataDxfId="9" dataCellStyle="常规 3"/>
+    <tableColumn id="3" xr3:uid="{9C16E955-26D0-4297-8D74-A4522556BE21}" name="核查方法" dataDxfId="8" dataCellStyle="常规 3"/>
+    <tableColumn id="4" xr3:uid="{EB078601-5671-43B0-A3BD-0F1A56DC7133}" name="分工" dataDxfId="7" dataCellStyle="常规 3"/>
+    <tableColumn id="5" xr3:uid="{40D12043-4EB9-4EAF-97A9-3E1AE0010E25}" name="输入关键词" dataDxfId="6" dataCellStyle="常规 3"/>
+    <tableColumn id="6" xr3:uid="{67E2662E-BFAC-4076-85EF-6DA44758E2A9}" name="数据源" dataDxfId="5" dataCellStyle="常规 3"/>
+    <tableColumn id="7" xr3:uid="{780EE4C9-FAB1-4FCF-9538-9980455C875B}" name="结果示例" dataDxfId="4" dataCellStyle="常规 3"/>
+    <tableColumn id="8" xr3:uid="{2DB7FC23-D9C2-48D2-9872-5E4B1F353096}" name="函数名" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{C2568AEC-F2A1-42F0-A274-D174158FEDBF}" name="返回值说明" dataDxfId="2" dataCellStyle="常规 3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2182,7 +2801,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2288,7 +2907,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2430,7 +3049,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2447,50 +3066,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF9952F-0606-4119-8381-8EA2BCD29B70}">
   <dimension ref="A1:J91"/>
-  <sheetFormatPr defaultRowHeight="35" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.06640625" style="14"/>
-    <col min="3" max="3" width="36.265625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="9.06640625" style="14"/>
-    <col min="5" max="5" width="34.73046875" style="30" customWidth="1"/>
-    <col min="6" max="7" width="9.06640625" style="14"/>
-    <col min="8" max="8" width="30.46484375" style="14" customWidth="1"/>
-    <col min="9" max="9" width="59.59765625" style="14" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="14"/>
+    <col min="1" max="1" width="10.25" style="12" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="12"/>
+    <col min="3" max="3" width="36.25" style="12" customWidth="1"/>
+    <col min="4" max="4" width="8" style="12" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="25" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="12"/>
+    <col min="7" max="7" width="10.25" style="12" customWidth="1"/>
+    <col min="8" max="8" width="30.5" style="12" customWidth="1"/>
+    <col min="9" max="9" width="59.625" style="12" customWidth="1"/>
+    <col min="10" max="16384" width="9.125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
+    <row r="2" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="26">
         <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -2510,13 +3131,13 @@
       <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="30" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
+    <row r="3" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="26">
         <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2536,13 +3157,13 @@
       <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="30" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
+    <row r="4" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="26">
         <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -2562,13 +3183,13 @@
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
+    <row r="5" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="26">
         <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -2588,13 +3209,13 @@
       <c r="H5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="30" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="15">
+    <row r="6" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="27">
         <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -2609,16 +3230,16 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="30" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="15">
+    <row r="7" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="27">
         <v>22</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2635,16 +3256,16 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="30" t="s">
         <v>31</v>
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="15">
+    <row r="8" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="27">
         <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -2661,16 +3282,16 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="30" t="s">
         <v>14</v>
       </c>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="15">
+    <row r="9" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="27">
         <v>22</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -2687,16 +3308,16 @@
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="30" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="15">
+    <row r="10" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="27">
         <v>22</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -2713,16 +3334,16 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="30" t="s">
         <v>38</v>
       </c>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
+    <row r="11" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="26">
         <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -2742,13 +3363,13 @@
       <c r="H11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="30" t="s">
         <v>42</v>
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2">
+    <row r="12" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="26">
         <v>25</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2768,13 +3389,13 @@
       <c r="H12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="30" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
+    <row r="13" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="26">
         <v>25</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -2794,13 +3415,13 @@
       <c r="H13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
+    <row r="14" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="26">
         <v>25</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -2820,13 +3441,13 @@
       <c r="H14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="30" t="s">
         <v>54</v>
       </c>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
+    <row r="15" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="26">
         <v>26</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -2838,21 +3459,21 @@
       <c r="D15" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="17"/>
+      <c r="F15" s="14"/>
       <c r="G15" s="3"/>
       <c r="H15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="30" t="s">
         <v>58</v>
       </c>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
+    <row r="16" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="26">
         <v>26</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -2872,13 +3493,13 @@
       <c r="H16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="30" t="s">
         <v>62</v>
       </c>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
+    <row r="17" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="26">
         <v>26</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2898,13 +3519,13 @@
       <c r="H17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="30" t="s">
         <v>66</v>
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
+    <row r="18" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="26">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -2924,13 +3545,13 @@
       <c r="H18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="30" t="s">
         <v>70</v>
       </c>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
+    <row r="19" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="26">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -2950,319 +3571,319 @@
       <c r="H19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="30" t="s">
         <v>74</v>
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="7">
+    <row r="20" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="28">
         <v>27</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>75</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="18" t="s">
+      <c r="G20" s="8"/>
+      <c r="H20" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="7">
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="28">
         <v>27</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>80</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="18" t="s">
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="J21" s="10"/>
-    </row>
-    <row r="22" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="7">
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="28">
         <v>27</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="18" t="s">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="7">
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="28">
         <v>27</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>88</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="18" t="s">
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="J23" s="10"/>
-    </row>
-    <row r="24" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="7">
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="28">
         <v>27</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>92</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="18" t="s">
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="2">
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="26">
         <v>28</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
       <c r="H25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I25" s="19" t="s">
+      <c r="I25" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="J25" s="21"/>
-    </row>
-    <row r="26" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="2">
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="26">
         <v>28</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
       <c r="H26" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I26" s="19" t="s">
+      <c r="I26" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="J26" s="19"/>
-    </row>
-    <row r="27" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="2">
+      <c r="J26" s="16"/>
+    </row>
+    <row r="27" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="26">
         <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="J27" s="21"/>
-    </row>
-    <row r="28" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="2">
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="26">
         <v>28</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
       <c r="H28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="J28" s="21"/>
-    </row>
-    <row r="29" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="22">
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="29">
         <v>29</v>
       </c>
-      <c r="B29" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
       <c r="H29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I29" s="23"/>
-      <c r="J29" s="24"/>
-    </row>
-    <row r="30" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="22">
+      <c r="I29" s="33"/>
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="29">
         <v>29</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
       <c r="H30" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="19" t="s">
+      <c r="I30" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="21"/>
-    </row>
-    <row r="31" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="22">
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="29">
         <v>29</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="19" t="s">
+      <c r="B31" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I31" s="19" t="s">
+      <c r="I31" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="J31" s="21"/>
-    </row>
-    <row r="32" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="2">
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="26">
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -3280,13 +3901,13 @@
       <c r="H32" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="30" t="s">
         <v>117</v>
       </c>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="2">
+    <row r="33" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="26">
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -3304,137 +3925,137 @@
       <c r="H33" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="30" t="s">
         <v>120</v>
       </c>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="2">
+    <row r="34" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="26">
         <v>31</v>
       </c>
-      <c r="B34" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="26" t="s">
+      <c r="B34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>121</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="27" t="s">
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="I34" s="26" t="s">
+      <c r="I34" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="J34" s="28"/>
-    </row>
-    <row r="35" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="2">
+      <c r="J34" s="23"/>
+    </row>
+    <row r="35" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="26">
         <v>31</v>
       </c>
-      <c r="B35" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="26" t="s">
+      <c r="B35" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>125</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="E35" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="27" t="s">
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="I35" s="26" t="s">
+      <c r="I35" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="J35" s="28"/>
-    </row>
-    <row r="36" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="2">
+      <c r="J35" s="23"/>
+    </row>
+    <row r="36" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="26">
         <v>31</v>
       </c>
-      <c r="B36" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="26" t="s">
+      <c r="B36" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>129</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E36" s="26" t="s">
+      <c r="E36" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="27" t="s">
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="I36" s="26" t="s">
+      <c r="I36" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="J36" s="28"/>
-    </row>
-    <row r="37" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="2">
+      <c r="J36" s="23"/>
+    </row>
+    <row r="37" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="26">
         <v>31</v>
       </c>
-      <c r="B37" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="26" t="s">
+      <c r="B37" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="26" t="s">
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="J37" s="28"/>
-    </row>
-    <row r="38" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="2">
+      <c r="J37" s="23"/>
+    </row>
+    <row r="38" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="26">
         <v>31</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="16" t="s">
         <v>134</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
       <c r="H38" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="30" t="s">
         <v>136</v>
       </c>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="2">
+    <row r="39" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="26">
         <v>32</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -3446,19 +4067,19 @@
       <c r="D39" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="16" t="s">
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I39" s="13"/>
+      <c r="I39" s="35"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="2">
+    <row r="40" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="26">
         <v>32</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -3475,16 +4096,16 @@
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="16" t="s">
+      <c r="H40" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="30" t="s">
         <v>140</v>
       </c>
       <c r="J40" s="5"/>
     </row>
-    <row r="41" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="2">
+    <row r="41" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="26">
         <v>32</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -3501,16 +4122,16 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="30" t="s">
         <v>144</v>
       </c>
       <c r="J41" s="5"/>
     </row>
-    <row r="42" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="2">
+    <row r="42" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="26">
         <v>33</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -3527,16 +4148,16 @@
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="30" t="s">
         <v>145</v>
       </c>
       <c r="J42" s="5"/>
     </row>
-    <row r="43" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="2">
+    <row r="43" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="26">
         <v>33</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -3556,11 +4177,11 @@
       <c r="H43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="3"/>
+      <c r="I43" s="30"/>
       <c r="J43" s="5"/>
     </row>
-    <row r="44" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="2">
+    <row r="44" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="26">
         <v>33</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -3577,16 +4198,16 @@
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="16" t="s">
+      <c r="H44" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="30" t="s">
         <v>146</v>
       </c>
       <c r="J44" s="5"/>
     </row>
-    <row r="45" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="2">
+    <row r="45" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="26">
         <v>33</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -3603,14 +4224,14 @@
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I45" s="3"/>
+      <c r="I45" s="30"/>
       <c r="J45" s="5"/>
     </row>
-    <row r="46" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="2">
+    <row r="46" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="26">
         <v>34</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -3622,19 +4243,19 @@
       <c r="D46" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
       <c r="H46" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I46" s="3"/>
+      <c r="I46" s="30"/>
       <c r="J46" s="5"/>
     </row>
-    <row r="47" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="2">
+    <row r="47" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="26">
         <v>34</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -3654,13 +4275,13 @@
       <c r="H47" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="30" t="s">
         <v>150</v>
       </c>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="2">
+    <row r="48" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="26">
         <v>34</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -3680,13 +4301,13 @@
       <c r="H48" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I48" s="30" t="s">
         <v>150</v>
       </c>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="2">
+    <row r="49" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="26">
         <v>34</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -3706,13 +4327,13 @@
       <c r="H49" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="30" t="s">
         <v>157</v>
       </c>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="2">
+    <row r="50" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="26">
         <v>34</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -3732,13 +4353,13 @@
       <c r="H50" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="30" t="s">
         <v>161</v>
       </c>
       <c r="J50" s="5"/>
     </row>
-    <row r="51" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="2">
+    <row r="51" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="26">
         <v>35</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -3750,19 +4371,19 @@
       <c r="D51" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
       <c r="H51" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I51" s="13"/>
+      <c r="I51" s="35"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="2">
+    <row r="52" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="26">
         <v>35</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -3782,13 +4403,13 @@
       <c r="H52" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="30" t="s">
         <v>165</v>
       </c>
       <c r="J52" s="5"/>
     </row>
-    <row r="53" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="2">
+    <row r="53" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="26">
         <v>35</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -3808,13 +4429,13 @@
       <c r="H53" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="I53" s="30" t="s">
         <v>168</v>
       </c>
       <c r="J53" s="5"/>
     </row>
-    <row r="54" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="2">
+    <row r="54" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="26">
         <v>36</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -3832,13 +4453,13 @@
       <c r="H54" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="30" t="s">
         <v>14</v>
       </c>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="2">
+    <row r="55" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="26">
         <v>36</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -3856,13 +4477,13 @@
       <c r="H55" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="I55" s="30" t="s">
         <v>17</v>
       </c>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="2">
+    <row r="56" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="26">
         <v>36</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -3880,11 +4501,11 @@
       <c r="H56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I56" s="3"/>
+      <c r="I56" s="30"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="2">
+    <row r="57" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="26">
         <v>36</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -3896,19 +4517,19 @@
       <c r="D57" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="12" t="s">
+      <c r="E57" s="11"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I57" s="30" t="s">
         <v>170</v>
       </c>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="2">
+    <row r="58" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="26">
         <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -3920,19 +4541,19 @@
       <c r="D58" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
       <c r="H58" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I58" s="13"/>
+      <c r="I58" s="35"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="2">
+    <row r="59" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="26">
         <v>37</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -3952,13 +4573,13 @@
       <c r="H59" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="I59" s="30" t="s">
         <v>174</v>
       </c>
       <c r="J59" s="5"/>
     </row>
-    <row r="60" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="2">
+    <row r="60" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="26">
         <v>37</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -3978,13 +4599,13 @@
       <c r="H60" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="I60" s="30" t="s">
         <v>178</v>
       </c>
       <c r="J60" s="5"/>
     </row>
-    <row r="61" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="2">
+    <row r="61" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="26">
         <v>38</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -4002,16 +4623,16 @@
       <c r="H61" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="I61" s="30" t="s">
         <v>179</v>
       </c>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="15">
+    <row r="62" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="27">
         <v>38</v>
       </c>
-      <c r="B62" s="29" t="s">
+      <c r="B62" s="24" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -4028,16 +4649,16 @@
       <c r="H62" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="I62" s="30" t="s">
         <v>183</v>
       </c>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="2">
+    <row r="63" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="26">
         <v>38</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="24" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -4052,11 +4673,11 @@
       <c r="H63" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="I63" s="13"/>
+      <c r="I63" s="35"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="2">
+    <row r="64" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="26">
         <v>39</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -4076,13 +4697,13 @@
       <c r="H64" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I64" s="30" t="s">
         <v>188</v>
       </c>
       <c r="J64" s="5"/>
     </row>
-    <row r="65" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="2">
+    <row r="65" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="26">
         <v>39</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -4102,13 +4723,13 @@
       <c r="H65" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" s="30" t="s">
         <v>192</v>
       </c>
       <c r="J65" s="5"/>
     </row>
-    <row r="66" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="2">
+    <row r="66" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="26">
         <v>39</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -4128,13 +4749,13 @@
       <c r="H66" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="I66" s="30" t="s">
         <v>196</v>
       </c>
       <c r="J66" s="5"/>
     </row>
-    <row r="67" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="2">
+    <row r="67" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="26">
         <v>39</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -4154,13 +4775,13 @@
       <c r="H67" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="30" t="s">
         <v>200</v>
       </c>
       <c r="J67" s="5"/>
     </row>
-    <row r="68" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="2">
+    <row r="68" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="26">
         <v>40</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -4177,14 +4798,14 @@
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I68" s="13"/>
+      <c r="I68" s="35"/>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="2">
+    <row r="69" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="26">
         <v>40</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -4201,16 +4822,16 @@
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I69" s="30" t="s">
         <v>204</v>
       </c>
       <c r="J69" s="5"/>
     </row>
-    <row r="70" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="2">
+    <row r="70" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="26">
         <v>40</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -4227,16 +4848,16 @@
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="16" t="s">
+      <c r="H70" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I70" s="30" t="s">
         <v>208</v>
       </c>
       <c r="J70" s="5"/>
     </row>
-    <row r="71" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="2">
+    <row r="71" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="26">
         <v>40</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -4253,16 +4874,16 @@
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="16" t="s">
+      <c r="H71" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="I71" s="30" t="s">
         <v>212</v>
       </c>
       <c r="J71" s="5"/>
     </row>
-    <row r="72" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="2">
+    <row r="72" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="26">
         <v>40</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -4279,16 +4900,16 @@
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="I72" s="30" t="s">
         <v>216</v>
       </c>
       <c r="J72" s="5"/>
     </row>
-    <row r="73" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="2">
+    <row r="73" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="26">
         <v>41</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -4308,11 +4929,11 @@
       <c r="H73" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I73" s="13"/>
+      <c r="I73" s="35"/>
       <c r="J73" s="6"/>
     </row>
-    <row r="74" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="2">
+    <row r="74" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="26">
         <v>41</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -4332,13 +4953,13 @@
       <c r="H74" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="I74" s="30" t="s">
         <v>218</v>
       </c>
       <c r="J74" s="5"/>
     </row>
-    <row r="75" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="2">
+    <row r="75" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="26">
         <v>41</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -4358,13 +4979,13 @@
       <c r="H75" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" s="30" t="s">
         <v>188</v>
       </c>
       <c r="J75" s="5"/>
     </row>
-    <row r="76" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="2">
+    <row r="76" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="26">
         <v>41</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -4384,13 +5005,13 @@
       <c r="H76" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="I76" s="30" t="s">
         <v>222</v>
       </c>
       <c r="J76" s="5"/>
     </row>
-    <row r="77" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="2">
+    <row r="77" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="26">
         <v>41</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -4410,13 +5031,13 @@
       <c r="H77" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" s="30" t="s">
         <v>226</v>
       </c>
       <c r="J77" s="5"/>
     </row>
-    <row r="78" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="2">
+    <row r="78" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="26">
         <v>41</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -4436,13 +5057,13 @@
       <c r="H78" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="I78" s="30" t="s">
         <v>230</v>
       </c>
       <c r="J78" s="5"/>
     </row>
-    <row r="79" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="2">
+    <row r="79" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="26">
         <v>41</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -4462,13 +5083,13 @@
       <c r="H79" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="I79" s="30" t="s">
         <v>234</v>
       </c>
       <c r="J79" s="5"/>
     </row>
-    <row r="80" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="2">
+    <row r="80" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="26">
         <v>41</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -4488,13 +5109,13 @@
       <c r="H80" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="I80" s="30" t="s">
         <v>238</v>
       </c>
       <c r="J80" s="5"/>
     </row>
-    <row r="81" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="2">
+    <row r="81" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="26">
         <v>41</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -4514,13 +5135,13 @@
       <c r="H81" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="30" t="s">
         <v>242</v>
       </c>
       <c r="J81" s="5"/>
     </row>
-    <row r="82" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="2">
+    <row r="82" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="26">
         <v>42</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -4535,16 +5156,16 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="16" t="s">
+      <c r="H82" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="I82" s="3" t="s">
+      <c r="I82" s="30" t="s">
         <v>245</v>
       </c>
       <c r="J82" s="5"/>
     </row>
-    <row r="83" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="2">
+    <row r="83" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="26">
         <v>42</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -4559,16 +5180,16 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
-      <c r="H83" s="16" t="s">
+      <c r="H83" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="I83" s="30" t="s">
         <v>248</v>
       </c>
       <c r="J83" s="5"/>
     </row>
-    <row r="84" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="2">
+    <row r="84" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="26">
         <v>42</v>
       </c>
       <c r="B84" s="4" t="s">
@@ -4585,16 +5206,16 @@
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="16" t="s">
+      <c r="H84" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="I84" s="30" t="s">
         <v>252</v>
       </c>
       <c r="J84" s="5"/>
     </row>
-    <row r="85" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="2">
+    <row r="85" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="26">
         <v>43</v>
       </c>
       <c r="B85" s="4" t="s">
@@ -4614,13 +5235,13 @@
       <c r="H85" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="I85" s="30" t="s">
         <v>256</v>
       </c>
       <c r="J85" s="5"/>
     </row>
-    <row r="86" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="2">
+    <row r="86" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="26">
         <v>43</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -4640,13 +5261,13 @@
       <c r="H86" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="I86" s="30" t="s">
         <v>260</v>
       </c>
       <c r="J86" s="5"/>
     </row>
-    <row r="87" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="2">
+    <row r="87" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="26">
         <v>43</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -4666,13 +5287,13 @@
       <c r="H87" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="I87" s="3" t="s">
+      <c r="I87" s="30" t="s">
         <v>264</v>
       </c>
       <c r="J87" s="5"/>
     </row>
-    <row r="88" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="2">
+    <row r="88" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="26">
         <v>43</v>
       </c>
       <c r="B88" s="4" t="s">
@@ -4692,13 +5313,13 @@
       <c r="H88" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="I88" s="30" t="s">
         <v>268</v>
       </c>
       <c r="J88" s="5"/>
     </row>
-    <row r="89" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="2">
+    <row r="89" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="26">
         <v>46</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -4715,16 +5336,16 @@
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
-      <c r="H89" s="16" t="s">
+      <c r="H89" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="I89" s="30" t="s">
         <v>271</v>
       </c>
       <c r="J89" s="5"/>
     </row>
-    <row r="90" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="2">
+    <row r="90" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="26">
         <v>46</v>
       </c>
       <c r="B90" s="4" t="s">
@@ -4741,36 +5362,36 @@
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="16" t="s">
+      <c r="H90" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I90" s="30" t="s">
         <v>275</v>
       </c>
       <c r="J90" s="5"/>
     </row>
-    <row r="91" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="2">
+    <row r="91" spans="1:10" ht="35.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="39">
         <v>46</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="3" t="s">
+      <c r="B91" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="16" t="s">
+      <c r="F91" s="41"/>
+      <c r="G91" s="41"/>
+      <c r="H91" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="I91" s="43" t="s">
         <v>279</v>
       </c>
       <c r="J91" s="5"/>
@@ -4779,5 +5400,8 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>